--- a/public/specialties.xlsx
+++ b/public/specialties.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hyamy010101\capacite-app-03\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\GitHub\capacite-app-05\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366E3E5D-AE04-4DBD-906D-843BD699786F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Spécialité</t>
   </si>
@@ -35,21 +36,6 @@
     <t>Besoin Pratique par Groupe</t>
   </si>
   <si>
-    <t>BTP TSIG</t>
-  </si>
-  <si>
-    <t>BTP PAO</t>
-  </si>
-  <si>
-    <t>BTP DDI</t>
-  </si>
-  <si>
-    <t>BTS DAI</t>
-  </si>
-  <si>
-    <t>BTS IG</t>
-  </si>
-  <si>
     <t>Besoin TP Spécifique par Groupe</t>
   </si>
   <si>
@@ -57,12 +43,111 @@
   </si>
   <si>
     <t>Besoin TP3 par Groupe</t>
+  </si>
+  <si>
+    <t>Technicien de soutien en informatique de gestion</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en informatique de gestion</t>
+  </si>
+  <si>
+    <t>Assistant(e) de direction</t>
+  </si>
+  <si>
+    <t>Technicien en secrétariat</t>
+  </si>
+  <si>
+    <t>Comptable d’entreprise</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en comptabilité et finances</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en commerce internationale</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en commerce</t>
+  </si>
+  <si>
+    <t>Technicien en formalités douanières</t>
+  </si>
+  <si>
+    <t>Technicien en commerce de distribution</t>
+  </si>
+  <si>
+    <t>Logisticien de distribution</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en marketing et multimédia</t>
+  </si>
+  <si>
+    <t>Agent d'entrepôt</t>
+  </si>
+  <si>
+    <t>Technicien en achats et approvisionnement</t>
+  </si>
+  <si>
+    <t>Vendeur (s) caissier (e) étalagiste</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en audiovisuel option  assistant réalisateur</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en audiovisuel option montage</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en audiovisuel  option prise de vue</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en audiovisuel  option prise de son</t>
+  </si>
+  <si>
+    <t>Technicien en photographie et traitement d'image</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en décoration et design d'intérieur</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en esthétique</t>
+  </si>
+  <si>
+    <t>Aide esthéticien(ne)</t>
+  </si>
+  <si>
+    <t>Coiffeur maquilleur</t>
+  </si>
+  <si>
+    <t>Technicien (ne) en esthétique</t>
+  </si>
+  <si>
+    <t>Agent de cuisine et de pâtisserie</t>
+  </si>
+  <si>
+    <t>Technicien de cuisine</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en cuisine</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en pâtisserie</t>
+  </si>
+  <si>
+    <t>Technicien de pâtisserie</t>
+  </si>
+  <si>
+    <t>Agent d'entretien en climatisation</t>
+  </si>
+  <si>
+    <t>1638 </t>
+  </si>
+  <si>
+    <t>458 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -99,13 +184,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -386,141 +484,657 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="6">
+        <v>800</v>
+      </c>
+      <c r="C2" s="4">
+        <v>926</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6">
+        <v>837</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1236</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4" s="6">
+        <v>1748</v>
+      </c>
+      <c r="C4" s="4">
+        <v>652</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5" s="7">
+        <v>836</v>
+      </c>
+      <c r="C5" s="5">
+        <v>700</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1052</v>
-      </c>
-      <c r="C2" s="2">
-        <v>879</v>
-      </c>
-      <c r="D2">
-        <v>350</v>
-      </c>
-      <c r="E2">
+      <c r="B6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2170</v>
+      </c>
+      <c r="C7" s="3">
+        <v>358</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2046</v>
+      </c>
+      <c r="C8" s="3">
+        <v>388</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1809</v>
+      </c>
+      <c r="C9" s="3">
+        <v>328</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1398</v>
+      </c>
+      <c r="C10" s="3">
+        <v>208</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3">
+        <v>933</v>
+      </c>
+      <c r="C11" s="6">
+        <v>753</v>
+      </c>
+      <c r="D11" s="2">
+        <v>370</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1401</v>
+      </c>
+      <c r="C12" s="3">
+        <v>348</v>
+      </c>
+      <c r="D12" s="1">
+        <v>488</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3">
+        <v>939</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1618</v>
+      </c>
+      <c r="D13" s="1">
+        <v>200</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="3">
+        <v>414</v>
+      </c>
+      <c r="C14" s="3">
+        <v>123</v>
+      </c>
+      <c r="D14" s="1">
+        <v>267</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1168</v>
+      </c>
+      <c r="C15" s="3">
+        <v>468</v>
+      </c>
+      <c r="D15" s="1">
+        <v>460</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3">
+        <v>655</v>
+      </c>
+      <c r="C16" s="3">
+        <v>338</v>
+      </c>
+      <c r="D16" s="1">
+        <v>285</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1433</v>
+      </c>
+      <c r="C17" s="3">
+        <v>188</v>
+      </c>
+      <c r="D17" s="1">
+        <v>274</v>
+      </c>
+      <c r="E17">
+        <v>34</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1421</v>
+      </c>
+      <c r="C18" s="3">
+        <v>408</v>
+      </c>
+      <c r="D18" s="1">
+        <v>95</v>
+      </c>
+      <c r="E18">
+        <v>35</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="3">
+        <v>1249</v>
+      </c>
+      <c r="C19" s="3">
+        <v>188</v>
+      </c>
+      <c r="D19" s="1">
+        <v>225</v>
+      </c>
+      <c r="E19">
+        <v>80</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1439</v>
+      </c>
+      <c r="C20" s="3">
+        <v>256</v>
+      </c>
+      <c r="D20" s="1">
+        <v>40</v>
+      </c>
+      <c r="E20">
+        <v>278</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="3">
+        <v>842</v>
+      </c>
+      <c r="C21" s="3">
+        <v>378</v>
+      </c>
+      <c r="D21" s="1">
+        <v>75</v>
+      </c>
+      <c r="E21">
+        <v>150</v>
+      </c>
+      <c r="F21">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="3">
+        <v>252</v>
+      </c>
+      <c r="C22" s="3">
+        <v>225</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1200</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="3">
+        <v>916</v>
+      </c>
+      <c r="C23" s="3">
+        <v>103</v>
+      </c>
+      <c r="D23" s="1">
+        <v>368</v>
+      </c>
+      <c r="E23">
+        <v>95</v>
+      </c>
+      <c r="F23">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="3">
+        <v>634</v>
+      </c>
+      <c r="C24" s="3">
+        <v>113</v>
+      </c>
+      <c r="D24" s="1">
+        <v>308</v>
+      </c>
+      <c r="E24">
+        <v>171</v>
+      </c>
+      <c r="F24">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
+        <v>610</v>
+      </c>
+      <c r="C25" s="3">
+        <v>123</v>
+      </c>
+      <c r="D25" s="1">
+        <v>353</v>
+      </c>
+      <c r="E25">
+        <v>50</v>
+      </c>
+      <c r="F25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1063</v>
+      </c>
+      <c r="C26" s="3">
+        <v>212</v>
+      </c>
+      <c r="D26" s="1">
+        <v>477</v>
+      </c>
+      <c r="E26">
+        <v>222</v>
+      </c>
+      <c r="F26">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="3">
+        <v>465</v>
+      </c>
+      <c r="C27" s="3">
+        <v>98</v>
+      </c>
+      <c r="D27" s="1">
+        <v>680</v>
+      </c>
+      <c r="E27">
+        <v>120</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="3">
+        <v>968</v>
+      </c>
+      <c r="C28" s="3">
+        <v>98</v>
+      </c>
+      <c r="D28" s="1">
+        <v>860</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1133</v>
+      </c>
+      <c r="C29" s="3">
+        <v>189</v>
+      </c>
+      <c r="D29" s="1">
         <v>100</v>
       </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1">
-        <v>928</v>
-      </c>
-      <c r="C3" s="2">
-        <v>879</v>
-      </c>
-      <c r="D3">
-        <v>220</v>
-      </c>
-      <c r="E3">
-        <v>200</v>
-      </c>
-      <c r="F3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1638</v>
-      </c>
-      <c r="C4" s="2">
-        <v>333</v>
-      </c>
-      <c r="D4">
-        <v>150</v>
-      </c>
-      <c r="E4">
-        <v>250</v>
-      </c>
-      <c r="F4">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1321</v>
-      </c>
-      <c r="C5" s="2">
-        <v>688</v>
-      </c>
-      <c r="D5">
-        <v>510</v>
-      </c>
-      <c r="E5">
-        <v>300</v>
-      </c>
-      <c r="F5">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>590</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1149</v>
-      </c>
-      <c r="D6">
-        <v>185</v>
-      </c>
-      <c r="E6">
-        <v>350</v>
-      </c>
-      <c r="F6">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="1"/>
-      <c r="D11" s="2"/>
+      <c r="E29">
+        <v>710</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1207</v>
+      </c>
+      <c r="C30" s="3">
+        <v>188</v>
+      </c>
+      <c r="D30" s="1">
+        <v>900</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="3">
+        <v>968</v>
+      </c>
+      <c r="C31" s="3">
+        <v>98</v>
+      </c>
+      <c r="D31" s="1">
+        <v>900</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="3">
+        <v>496</v>
+      </c>
+      <c r="C32" s="3">
+        <v>30</v>
+      </c>
+      <c r="D32" s="1">
+        <v>794</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/specialties.xlsx
+++ b/public/specialties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\GitHub\capacite-app-05\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366E3E5D-AE04-4DBD-906D-843BD699786F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A263FD31-EE9A-47DD-9FF9-CB4CF7217ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1067,10 +1067,10 @@
         <v>189</v>
       </c>
       <c r="D29" s="1">
+        <v>710</v>
+      </c>
+      <c r="E29">
         <v>100</v>
-      </c>
-      <c r="E29">
-        <v>710</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1087,10 +1087,10 @@
         <v>188</v>
       </c>
       <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30">
         <v>900</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1107,10 +1107,10 @@
         <v>98</v>
       </c>
       <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31">
         <v>900</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
       </c>
       <c r="F31">
         <v>0</v>

--- a/public/specialties.xlsx
+++ b/public/specialties.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9F8CE7-6380-499E-9251-8AD233F7AC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EB4512-1D6D-48A2-943C-EC2930F218D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/public/specialties.xlsx
+++ b/public/specialties.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hichembensoltan\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EB4512-1D6D-48A2-943C-EC2930F218D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Spécialité</t>
   </si>
@@ -156,13 +155,28 @@
     <t>Animateur de Jardin d'Enfants 1</t>
   </si>
   <si>
-    <t>Auxilière de vie</t>
+    <t>Auxiliaire de vie</t>
+  </si>
+  <si>
+    <t>Technicien supérieur en maintenance des systèmes mécatroniques et apès vente de l'automobile</t>
+  </si>
+  <si>
+    <t>Technicien en mécanique et électricité automobile</t>
+  </si>
+  <si>
+    <t>réparateur automobile essence et diesel</t>
+  </si>
+  <si>
+    <t>Aide mécanicien de véhicules légers</t>
+  </si>
+  <si>
+    <t>Aide mécanicien de poids lourds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -499,19 +513,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="54.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -551,7 +565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -571,7 +585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -591,7 +605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -611,7 +625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -631,7 +645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -651,7 +665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -671,7 +685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -691,7 +705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -711,7 +725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -731,7 +745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -751,7 +765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -771,7 +785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -791,7 +805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -811,7 +825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -831,7 +845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -851,7 +865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -871,7 +885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -891,7 +905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -911,7 +925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -931,7 +945,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -951,7 +965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -971,7 +985,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -991,7 +1005,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1011,7 +1025,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1031,7 +1045,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1051,7 +1065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1071,7 +1085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -1091,7 +1105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1111,7 +1125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -1131,7 +1145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -1151,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -1171,7 +1185,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -1191,7 +1205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>41</v>
       </c>
@@ -1211,7 +1225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -1231,7 +1245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>43</v>
       </c>
@@ -1243,6 +1257,112 @@
       </c>
       <c r="D37" s="1">
         <v>410</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3">
+        <v>849</v>
+      </c>
+      <c r="C38" s="3">
+        <v>146</v>
+      </c>
+      <c r="D38" s="1">
+        <v>78</v>
+      </c>
+      <c r="E38">
+        <v>60</v>
+      </c>
+      <c r="F38">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1047</v>
+      </c>
+      <c r="C39" s="3">
+        <v>48</v>
+      </c>
+      <c r="D39" s="1">
+        <v>108</v>
+      </c>
+      <c r="E39">
+        <v>64</v>
+      </c>
+      <c r="F39">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="3">
+        <v>757</v>
+      </c>
+      <c r="C40" s="3">
+        <v>54</v>
+      </c>
+      <c r="D40" s="1">
+        <v>66</v>
+      </c>
+      <c r="E40">
+        <v>108</v>
+      </c>
+      <c r="F40">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="3">
+        <v>575</v>
+      </c>
+      <c r="C41" s="3">
+        <v>24</v>
+      </c>
+      <c r="D41" s="1">
+        <v>24</v>
+      </c>
+      <c r="E41">
+        <v>14</v>
+      </c>
+      <c r="F41">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="3">
+        <v>585</v>
+      </c>
+      <c r="C42" s="3">
+        <v>0</v>
+      </c>
+      <c r="D42" s="1">
+        <v>24</v>
+      </c>
+      <c r="E42">
+        <v>32</v>
+      </c>
+      <c r="F42">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
